--- a/artfynd/A 48272-2024 artfynd.xlsx
+++ b/artfynd/A 48272-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>297036</v>
+        <v>64409410</v>
       </c>
       <c r="B2" t="n">
-        <v>89387</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kastfjärden, Vb</t>
+          <t>Lillavan, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>802763.5094384211</v>
+        <v>803095</v>
       </c>
       <c r="R2" t="n">
-        <v>7175258.263137029</v>
+        <v>7175344</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +746,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +760,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,22 +772,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64409410</v>
+        <v>73014855</v>
       </c>
       <c r="B3" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,43 +790,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillavan, Vb</t>
+          <t>Kastfjärden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>803095.3567439134</v>
+        <v>803124</v>
       </c>
       <c r="R3" t="n">
-        <v>7175343.847555632</v>
+        <v>7175115</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,22 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,34 +858,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>64409194</v>
+        <v>120791510</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,43 +887,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillavan, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>803233.7260975282</v>
+        <v>803222</v>
       </c>
       <c r="R4" t="n">
-        <v>7175091.245822089</v>
+        <v>7175258</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,34 +969,48 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Lill Eilertsen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Lill Eilertsen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>64409355</v>
+        <v>64659199</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,37 +1018,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1106</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillavan, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>803126.4038742164</v>
+        <v>803126</v>
       </c>
       <c r="R5" t="n">
-        <v>7175327.926666581</v>
+        <v>7175322</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,27 +1081,18 @@
           <t>2013-08-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-08-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1133,22 +1104,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>per-erik mukka, Gudrun Norstedt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>64409270</v>
+        <v>297036</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,43 +1122,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillavan, Vb</t>
+          <t>Kastfjärden, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>803205.0974038867</v>
+        <v>802764</v>
       </c>
       <c r="R6" t="n">
-        <v>7175273.092713339</v>
+        <v>7175258</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,22 +1176,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-12-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,7 +1190,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1252,66 +1201,55 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>64659199</v>
+        <v>73014862</v>
       </c>
       <c r="B7" t="n">
-        <v>89588</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1106</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillavan, Vb</t>
+          <t>Kastfjärden, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>803125.6755793958</v>
+        <v>802911</v>
       </c>
       <c r="R7" t="n">
-        <v>7175322.230240447</v>
+        <v>7175273</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,22 +1273,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,34 +1287,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>per-erik mukka, Gudrun Norstedt</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73014862</v>
+        <v>73014863</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>802911.0190455145</v>
+        <v>803132</v>
       </c>
       <c r="R8" t="n">
-        <v>7175273.035612365</v>
+        <v>7175354</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1451,19 +1373,9 @@
           <t>2018-09-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2018-09-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,15 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>73014855</v>
+        <v>120791525</v>
       </c>
       <c r="B9" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,37 +1413,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kastfjärden, Vb</t>
+          <t>Lillavan, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>803123.940944857</v>
+        <v>803222</v>
       </c>
       <c r="R9" t="n">
-        <v>7175114.847901584</v>
+        <v>7175258</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,22 +1467,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,31 +1483,46 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Lill Eilertsen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Lill Eilertsen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>73014863</v>
+        <v>120791562</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,17 +1550,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kastfjärden, Vb</t>
+          <t>Lillavan, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>803132.0180603528</v>
+        <v>803016</v>
       </c>
       <c r="R10" t="n">
-        <v>7175354.011009545</v>
+        <v>7175167</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1672,22 +1584,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,31 +1600,46 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Lill Eilertsen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Lill Eilertsen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120791510</v>
+        <v>120791793</v>
       </c>
       <c r="B11" t="n">
-        <v>90973</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,48 +1647,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lillavan, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>803222</v>
+        <v>803117</v>
       </c>
       <c r="R11" t="n">
-        <v>7175258</v>
+        <v>7175124</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1850,15 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120791525</v>
+        <v>64409355</v>
       </c>
       <c r="B12" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,37 +1764,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lillavan, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>803222</v>
+        <v>803126</v>
       </c>
       <c r="R12" t="n">
-        <v>7175258</v>
+        <v>7175328</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1920,12 +1821,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2013-08-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2013-08-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,283 +1837,19 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lill Eilertsen</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lill Eilertsen</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>120791562</v>
-      </c>
-      <c r="B13" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Lillavan, Vb</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>803016</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7175167</v>
-      </c>
-      <c r="S13" t="n">
-        <v>20</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Bureå</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2024-10-31</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2024-10-31</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Lill Eilertsen</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Lill Eilertsen</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>120791793</v>
-      </c>
-      <c r="B14" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Lillavan, Vb</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>803117</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7175124</v>
-      </c>
-      <c r="S14" t="n">
-        <v>20</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Bureå</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2024-10-31</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2024-10-31</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Lill Eilertsen</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Lill Eilertsen</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48272-2024 artfynd.xlsx
+++ b/artfynd/A 48272-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64409410</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -873,6 +883,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73014855</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120791510</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64659199</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/297036</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73014862</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73014863</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1516,6 +1556,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120791525</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1633,6 +1678,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120791562</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1750,6 +1800,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120791793</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1850,8 +1905,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64409355</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 48272-2024 artfynd.xlsx
+++ b/artfynd/A 48272-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>64409355</v>
+        <v>135645786</v>
       </c>
       <c r="B12" t="n">
-        <v>57953</v>
+        <v>92016</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,40 +1819,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillavan, Vb</t>
+          <t>Kastfjärden , Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>803126</v>
+        <v>803074</v>
       </c>
       <c r="R12" t="n">
-        <v>7175328</v>
+        <v>7175363</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1876,12 +1876,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,24 +1890,582 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135645786</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>64409355</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lillavan, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>803126</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7175328</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2013-08-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2013-08-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/64409355</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135645813</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kastfjärden , Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>803060</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7175371</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135645813</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135645839</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kastfjärden , Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>803088</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7175383</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135645839</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135645949</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kastfjärden , Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>803125</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7175289</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosök genom skalning av undertryckt gran</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135645949</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135645738</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kastfjärden , Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>803062</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7175366</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135645738</t>
         </is>
       </c>
     </row>
@@ -1924,6 +2482,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48272-2024 artfynd.xlsx
+++ b/artfynd/A 48272-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1811,7 +1811,7 @@
         <v>135645786</v>
       </c>
       <c r="B12" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>64409355</v>
+        <v>135688020</v>
       </c>
       <c r="B13" t="n">
-        <v>57953</v>
+        <v>92043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1925,37 +1925,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillavan, Vb</t>
+          <t>Lill-Avan, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>803126</v>
+        <v>803063</v>
       </c>
       <c r="R13" t="n">
-        <v>7175328</v>
+        <v>7175372</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1982,12 +1986,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1996,6 +2000,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2007,22 +2012,22 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64409355</t>
+          <t>https://artportalen.se/Sighting/135688020</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135645813</v>
+        <v>135688252</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>92043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,45 +2035,44 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kastfjärden , Vb</t>
+          <t>Lill-Avan, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>803060</v>
+        <v>803058</v>
       </c>
       <c r="R14" t="n">
-        <v>7175371</v>
+        <v>7175374</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2100,44 +2104,40 @@
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645813</t>
+          <t>https://artportalen.se/Sighting/135688252</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135645839</v>
+        <v>135688431</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>92043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,45 +2145,44 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kastfjärden , Vb</t>
+          <t>Lill-Avan, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>803088</v>
+        <v>803098</v>
       </c>
       <c r="R15" t="n">
-        <v>7175383</v>
+        <v>7175108</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2215,44 +2214,40 @@
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645839</t>
+          <t>https://artportalen.se/Sighting/135688431</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135645949</v>
+        <v>135688456</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>92043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2260,45 +2255,44 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kastfjärden , Vb</t>
+          <t>Lill-Avan, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>803125</v>
+        <v>803106</v>
       </c>
       <c r="R16" t="n">
-        <v>7175289</v>
+        <v>7175106</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2330,44 +2324,40 @@
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosök genom skalning av undertryckt gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645949</t>
+          <t>https://artportalen.se/Sighting/135688456</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135645738</v>
+        <v>135688039</v>
       </c>
       <c r="B17" t="n">
-        <v>99242</v>
+        <v>92387</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2375,41 +2365,44 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kastfjärden , Vb</t>
+          <t>Lill-Avan, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>803062</v>
+        <v>803063</v>
       </c>
       <c r="R17" t="n">
-        <v>7175366</v>
+        <v>7175372</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2439,6 +2432,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>växte på ullticka, runda porer, utdragna mot kanten av lågan, fruktkroppen gulnade kraftigt efter torkning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2454,18 +2452,1950 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135688039</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135687531</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>803217</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7175187</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687531</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135687802</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79462</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>803151</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7175309</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687802</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135687873</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>803135</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7175325</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>äldre hackat hål i basen på en gran</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687873</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135687922</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>803129</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7175326</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>färskt hål i gran</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687922</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135688397</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>802998</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7175117</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>hål i högstubbe</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135688397</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>64409355</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lillavan, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>803126</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7175328</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2013-08-15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2013-08-15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64409355</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135645813</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kastfjärden , Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>803060</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7175371</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135645813</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135645839</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kastfjärden , Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>803088</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7175383</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135645839</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135645949</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kastfjärden , Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>803125</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7175289</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Födosök genom skalning av undertryckt gran</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135645949</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135687640</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>803157</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7175310</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>barksprätt på en gammal gran samt en barkskalad undertryckt gran</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687640</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135687713</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>803170</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7175011</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687713</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135687761</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>803200</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7175276</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687761</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135687832</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>803153</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7175319</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687832</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135688412</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>803078</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7175102</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135688412</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135688478</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>803122</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7175091</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135688478</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135645738</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kastfjärden , Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>803062</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7175366</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135645738</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135688282</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>803056</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7175365</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>ca 2x1 m med bladrosetter och 5st överblommade/blommande stänglar</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135688282</t>
         </is>
       </c>
     </row>
@@ -2487,6 +4417,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48272-2024 artfynd.xlsx
+++ b/artfynd/A 48272-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73014855</v>
+        <v>135710343</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>91993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>803124</v>
+        <v>803075</v>
       </c>
       <c r="R3" t="n">
-        <v>7175115</v>
+        <v>7175346</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,12 +854,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,27 +884,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73014855</t>
+          <t>https://artportalen.se/Sighting/135710343</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120791510</v>
+        <v>73014855</v>
       </c>
       <c r="B4" t="n">
-        <v>92208</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,51 +912,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillavan, Vb</t>
+          <t>Kastfjärden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>803222</v>
+        <v>803124</v>
       </c>
       <c r="R4" t="n">
-        <v>7175258</v>
+        <v>7175115</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,12 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,51 +982,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lill Eilertsen</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lill Eilertsen</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120791510</t>
+          <t>https://artportalen.se/Sighting/73014855</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>64659199</v>
+        <v>120791510</v>
       </c>
       <c r="B5" t="n">
-        <v>92134</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,43 +1014,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1106</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillavan, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>803126</v>
+        <v>803222</v>
       </c>
       <c r="R5" t="n">
-        <v>7175322</v>
+        <v>7175258</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,34 +1096,53 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Lill Eilertsen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>per-erik mukka, Gudrun Norstedt</t>
+          <t>Lill Eilertsen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64659199</t>
+          <t>https://artportalen.se/Sighting/120791510</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>297036</v>
+        <v>64659199</v>
       </c>
       <c r="B6" t="n">
-        <v>91905</v>
+        <v>92134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,37 +1150,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kastfjärden, Vb</t>
+          <t>Lillavan, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>802764</v>
+        <v>803126</v>
       </c>
       <c r="R6" t="n">
-        <v>7175258</v>
+        <v>7175322</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,12 +1210,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2000-01-01</t>
+          <t>2013-08-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2005-12-31</t>
+          <t>2013-08-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,6 +1224,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1226,22 +1236,22 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>per-erik mukka, Gudrun Norstedt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/297036</t>
+          <t>https://artportalen.se/Sighting/64659199</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73014862</v>
+        <v>297036</v>
       </c>
       <c r="B7" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,21 +1259,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1273,13 +1283,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>802911</v>
+        <v>802764</v>
       </c>
       <c r="R7" t="n">
-        <v>7175273</v>
+        <v>7175258</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1313,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
+          <t>2005-12-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,24 +1333,24 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73014862</t>
+          <t>https://artportalen.se/Sighting/297036</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73014863</v>
+        <v>73014862</v>
       </c>
       <c r="B8" t="n">
         <v>91909</v>
@@ -1375,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>803132</v>
+        <v>802911</v>
       </c>
       <c r="R8" t="n">
-        <v>7175354</v>
+        <v>7175273</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1436,13 +1446,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73014863</t>
+          <t>https://artportalen.se/Sighting/73014862</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120791525</v>
+        <v>73014863</v>
       </c>
       <c r="B9" t="n">
         <v>91909</v>
@@ -1473,17 +1483,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillavan, Vb</t>
+          <t>Kastfjärden, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>803222</v>
+        <v>803132</v>
       </c>
       <c r="R9" t="n">
-        <v>7175258</v>
+        <v>7175354</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,12 +1517,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,48 +1533,28 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lill Eilertsen</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lill Eilertsen</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120791525</t>
+          <t>https://artportalen.se/Sighting/73014863</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120791562</v>
+        <v>120791525</v>
       </c>
       <c r="B10" t="n">
         <v>91909</v>
@@ -1599,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>803016</v>
+        <v>803222</v>
       </c>
       <c r="R10" t="n">
-        <v>7175167</v>
+        <v>7175258</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1680,13 +1670,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120791562</t>
+          <t>https://artportalen.se/Sighting/120791525</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120791793</v>
+        <v>120791562</v>
       </c>
       <c r="B11" t="n">
         <v>91909</v>
@@ -1721,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>803117</v>
+        <v>803016</v>
       </c>
       <c r="R11" t="n">
-        <v>7175124</v>
+        <v>7175167</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1802,16 +1792,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120791793</t>
+          <t>https://artportalen.se/Sighting/120791562</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135645786</v>
+        <v>120791793</v>
       </c>
       <c r="B12" t="n">
-        <v>92043</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1837,22 +1827,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kastfjärden , Vb</t>
+          <t>Lillavan, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>803074</v>
+        <v>803117</v>
       </c>
       <c r="R12" t="n">
-        <v>7175363</v>
+        <v>7175124</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1876,12 +1863,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,31 +1877,50 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Lill Eilertsen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Lill Eilertsen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645786</t>
+          <t>https://artportalen.se/Sighting/120791793</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135688020</v>
+        <v>135645786</v>
       </c>
       <c r="B13" t="n">
         <v>92043</v>
@@ -1943,26 +1949,22 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill-Avan, Vb</t>
+          <t>Kastfjärden , Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>803063</v>
+        <v>803074</v>
       </c>
       <c r="R13" t="n">
-        <v>7175372</v>
+        <v>7175363</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2007,24 +2009,24 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135688020</t>
+          <t>https://artportalen.se/Sighting/135645786</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135688252</v>
+        <v>135688020</v>
       </c>
       <c r="B14" t="n">
         <v>92043</v>
@@ -2066,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>803058</v>
+        <v>803063</v>
       </c>
       <c r="R14" t="n">
-        <v>7175374</v>
+        <v>7175372</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,13 +2130,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135688252</t>
+          <t>https://artportalen.se/Sighting/135688020</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135688431</v>
+        <v>135688252</v>
       </c>
       <c r="B15" t="n">
         <v>92043</v>
@@ -2176,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>803098</v>
+        <v>803058</v>
       </c>
       <c r="R15" t="n">
-        <v>7175108</v>
+        <v>7175374</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2238,13 +2240,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135688431</t>
+          <t>https://artportalen.se/Sighting/135688252</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135688456</v>
+        <v>135688431</v>
       </c>
       <c r="B16" t="n">
         <v>92043</v>
@@ -2286,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>803106</v>
+        <v>803098</v>
       </c>
       <c r="R16" t="n">
-        <v>7175106</v>
+        <v>7175108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2348,38 +2350,38 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135688456</t>
+          <t>https://artportalen.se/Sighting/135688431</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135688039</v>
+        <v>135688456</v>
       </c>
       <c r="B17" t="n">
-        <v>92387</v>
+        <v>92043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2396,10 +2398,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>803063</v>
+        <v>803106</v>
       </c>
       <c r="R17" t="n">
-        <v>7175372</v>
+        <v>7175106</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2434,11 +2436,6 @@
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>växte på ullticka, runda porer, utdragna mot kanten av lågan, fruktkroppen gulnade kraftigt efter torkning</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2463,58 +2460,51 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135688039</t>
+          <t>https://artportalen.se/Sighting/135688456</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135687531</v>
+        <v>135710332</v>
       </c>
       <c r="B18" t="n">
-        <v>92006</v>
+        <v>92043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-Avan, Vb</t>
+          <t>Kastfjärden, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>803217</v>
+        <v>803214</v>
       </c>
       <c r="R18" t="n">
-        <v>7175187</v>
+        <v>7175033</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2544,87 +2534,89 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135687531</t>
+          <t>https://artportalen.se/Sighting/135710332</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135687802</v>
+        <v>135710334</v>
       </c>
       <c r="B19" t="n">
-        <v>79462</v>
+        <v>92043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6434</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-Avan, Vb</t>
+          <t>Kastfjärden, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>803151</v>
+        <v>803222</v>
       </c>
       <c r="R19" t="n">
-        <v>7175309</v>
+        <v>7175107</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2654,88 +2646,89 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135687802</t>
+          <t>https://artportalen.se/Sighting/135710334</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135687873</v>
+        <v>135710335</v>
       </c>
       <c r="B20" t="n">
-        <v>57977</v>
+        <v>92043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill-Avan, Vb</t>
+          <t>Kastfjärden, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>803135</v>
+        <v>803229</v>
       </c>
       <c r="R20" t="n">
-        <v>7175325</v>
+        <v>7175188</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2765,14 +2758,19 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>äldre hackat hål i basen på en gran</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2787,70 +2785,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135687873</t>
+          <t>https://artportalen.se/Sighting/135710335</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135687922</v>
+        <v>135710338</v>
       </c>
       <c r="B21" t="n">
-        <v>57977</v>
+        <v>92043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lill-Avan, Vb</t>
+          <t>Kastfjärden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>803129</v>
+        <v>803200</v>
       </c>
       <c r="R21" t="n">
-        <v>7175326</v>
+        <v>7175245</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2880,14 +2870,19 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>färskt hål i gran</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2902,70 +2897,62 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135687922</t>
+          <t>https://artportalen.se/Sighting/135710338</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135688397</v>
+        <v>135710339</v>
       </c>
       <c r="B22" t="n">
-        <v>57977</v>
+        <v>92043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lill-Avan, Vb</t>
+          <t>Kastfjärden, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>802998</v>
+        <v>803115</v>
       </c>
       <c r="R22" t="n">
-        <v>7175117</v>
+        <v>7175342</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2995,14 +2982,19 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>hål i högstubbe</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3017,27 +3009,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135688397</t>
+          <t>https://artportalen.se/Sighting/135710339</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>64409355</v>
+        <v>135710340</v>
       </c>
       <c r="B23" t="n">
-        <v>57953</v>
+        <v>92043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3045,37 +3037,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lillavan, Vb</t>
+          <t>Kastfjärden, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>803126</v>
+        <v>803099</v>
       </c>
       <c r="R23" t="n">
-        <v>7175328</v>
+        <v>7175372</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3102,12 +3091,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3122,27 +3121,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64409355</t>
+          <t>https://artportalen.se/Sighting/135710340</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135645813</v>
+        <v>135710345</v>
       </c>
       <c r="B24" t="n">
-        <v>57980</v>
+        <v>92043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3150,45 +3149,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kastfjärden , Vb</t>
+          <t>Kastfjärden, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>803060</v>
+        <v>803061</v>
       </c>
       <c r="R24" t="n">
-        <v>7175371</v>
+        <v>7175203</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3215,21 +3206,26 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Barksprätt på gran</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>
@@ -3237,73 +3233,72 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645813</t>
+          <t>https://artportalen.se/Sighting/135710345</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135645839</v>
+        <v>135688039</v>
       </c>
       <c r="B25" t="n">
-        <v>57980</v>
+        <v>92387</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kastfjärden , Vb</t>
+          <t>Lill-Avan, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>803088</v>
+        <v>803063</v>
       </c>
       <c r="R25" t="n">
-        <v>7175383</v>
+        <v>7175372</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3337,88 +3332,88 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Barksprätt på gran</t>
+          <t>växte på ullticka, runda porer, utdragna mot kanten av lågan, fruktkroppen gulnade kraftigt efter torkning</t>
         </is>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645839</t>
+          <t>https://artportalen.se/Sighting/135688039</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135645949</v>
+        <v>135687531</v>
       </c>
       <c r="B26" t="n">
-        <v>57980</v>
+        <v>92006</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kastfjärden , Vb</t>
+          <t>Lill-Avan, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>803125</v>
+        <v>803217</v>
       </c>
       <c r="R26" t="n">
-        <v>7175289</v>
+        <v>7175187</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3450,76 +3445,71 @@
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Födosök genom skalning av undertryckt gran</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645949</t>
+          <t>https://artportalen.se/Sighting/135687531</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135687640</v>
+        <v>135687802</v>
       </c>
       <c r="B27" t="n">
-        <v>57980</v>
+        <v>79462</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3527,10 +3517,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>803157</v>
+        <v>803151</v>
       </c>
       <c r="R27" t="n">
-        <v>7175310</v>
+        <v>7175309</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3565,17 +3555,13 @@
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>barksprätt på en gammal gran samt en barkskalad undertryckt gran</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3593,33 +3579,33 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135687640</t>
+          <t>https://artportalen.se/Sighting/135687802</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135687713</v>
+        <v>135687873</v>
       </c>
       <c r="B28" t="n">
-        <v>57980</v>
+        <v>57977</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3632,7 +3618,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3642,10 +3628,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>803170</v>
+        <v>803135</v>
       </c>
       <c r="R28" t="n">
-        <v>7175011</v>
+        <v>7175325</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3682,14 +3668,14 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>äldre hackat hål i basen på en gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="b">
         <v>0</v>
@@ -3708,33 +3694,33 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135687713</t>
+          <t>https://artportalen.se/Sighting/135687873</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135687761</v>
+        <v>135687922</v>
       </c>
       <c r="B29" t="n">
-        <v>57980</v>
+        <v>57977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3757,10 +3743,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>803200</v>
+        <v>803129</v>
       </c>
       <c r="R29" t="n">
-        <v>7175276</v>
+        <v>7175326</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3797,14 +3783,14 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>färskt hål i gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="b">
         <v>0</v>
@@ -3823,33 +3809,33 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135687761</t>
+          <t>https://artportalen.se/Sighting/135687922</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135687832</v>
+        <v>135688397</v>
       </c>
       <c r="B30" t="n">
-        <v>57980</v>
+        <v>57977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3872,10 +3858,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>803153</v>
+        <v>802998</v>
       </c>
       <c r="R30" t="n">
-        <v>7175319</v>
+        <v>7175117</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3912,14 +3898,14 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hål i högstubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="b">
         <v>0</v>
@@ -3938,16 +3924,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135687832</t>
+          <t>https://artportalen.se/Sighting/135688397</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135688412</v>
+        <v>64409355</v>
       </c>
       <c r="B31" t="n">
-        <v>57980</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3975,22 +3961,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lill-Avan, Vb</t>
+          <t>Lillavan, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>803078</v>
+        <v>803126</v>
       </c>
       <c r="R31" t="n">
-        <v>7175102</v>
+        <v>7175328</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4017,24 +3998,19 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2013-08-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
+          <t>2013-08-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="b">
         <v>0</v>
@@ -4047,19 +4023,19 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135688412</t>
+          <t>https://artportalen.se/Sighting/64409355</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135688478</v>
+        <v>135645813</v>
       </c>
       <c r="B32" t="n">
         <v>57980</v>
@@ -4092,23 +4068,23 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lill-Avan, Vb</t>
+          <t>Kastfjärden , Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>803122</v>
+        <v>803060</v>
       </c>
       <c r="R32" t="n">
-        <v>7175091</v>
+        <v>7175371</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4142,7 +4118,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>Barksprätt på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4157,55 +4133,59 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135688478</t>
+          <t>https://artportalen.se/Sighting/135645813</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135645738</v>
+        <v>135645839</v>
       </c>
       <c r="B33" t="n">
-        <v>99269</v>
+        <v>57980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4213,10 +4193,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>803062</v>
+        <v>803088</v>
       </c>
       <c r="R33" t="n">
-        <v>7175366</v>
+        <v>7175383</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4251,13 +4231,17 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4275,66 +4259,62 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645738</t>
+          <t>https://artportalen.se/Sighting/135645839</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135688282</v>
+        <v>135645949</v>
       </c>
       <c r="B34" t="n">
-        <v>99269</v>
+        <v>57980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lill-Avan, Vb</t>
+          <t>Kastfjärden , Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>803056</v>
+        <v>803125</v>
       </c>
       <c r="R34" t="n">
-        <v>7175365</v>
+        <v>7175289</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4368,34 +4348,1548 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ca 2x1 m med bladrosetter och 5st överblommade/blommande stänglar</t>
+          <t>Födosök genom skalning av undertryckt gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135645949</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135687640</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>803157</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7175310</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>barksprätt på en gammal gran samt en barkskalad undertryckt gran</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687640</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135687713</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>803170</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7175011</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687713</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135687761</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>803200</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7175276</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687761</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135687832</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>803153</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7175319</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687832</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135688412</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>803078</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7175102</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135688412</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135688478</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>803122</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7175091</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135688478</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135710336</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kastfjärden, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>803217</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7175218</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack bild</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135710336</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135710347</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kastfjärden, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>803041</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7175192</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Skalad gran äldre</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135710347</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135710333</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kastfjärden, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>803214</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7175033</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135710333</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135710348</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kastfjärden, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>803118</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7175079</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135710348</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135645738</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kastfjärden , Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>803062</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7175366</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135645738</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135688282</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>803056</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7175365</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>ca 2x1 m med bladrosetter och 5st överblommade/blommande stänglar</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135688282</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135710342</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kastfjärden, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>803062</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7175357</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Överblommad, många bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135710342</t>
         </is>
       </c>
     </row>
@@ -4434,6 +5928,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48272-2024 artfynd.xlsx
+++ b/artfynd/A 48272-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73014855</v>
+        <v>135710343</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>91998</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>803124</v>
+        <v>803075</v>
       </c>
       <c r="R3" t="n">
-        <v>7175115</v>
+        <v>7175346</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,12 +854,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,27 +884,31 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73014855</t>
+          <t>https://artportalen.se/Sighting/135710343</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120791510</v>
+        <v>73014855</v>
       </c>
       <c r="B4" t="n">
-        <v>92208</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,51 +916,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillavan, Vb</t>
+          <t>Kastfjärden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>803222</v>
+        <v>803124</v>
       </c>
       <c r="R4" t="n">
-        <v>7175258</v>
+        <v>7175115</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,12 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,51 +986,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lill Eilertsen</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lill Eilertsen</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120791510</t>
+          <t>https://artportalen.se/Sighting/73014855</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>64659199</v>
+        <v>120791510</v>
       </c>
       <c r="B5" t="n">
-        <v>92134</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,43 +1018,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1106</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillavan, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>803126</v>
+        <v>803222</v>
       </c>
       <c r="R5" t="n">
-        <v>7175322</v>
+        <v>7175258</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,12 +1086,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,34 +1100,53 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Lill Eilertsen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>per-erik mukka, Gudrun Norstedt</t>
+          <t>Lill Eilertsen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64659199</t>
+          <t>https://artportalen.se/Sighting/120791510</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>297036</v>
+        <v>64659199</v>
       </c>
       <c r="B6" t="n">
-        <v>91905</v>
+        <v>92134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,37 +1154,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kastfjärden, Vb</t>
+          <t>Lillavan, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>802764</v>
+        <v>803126</v>
       </c>
       <c r="R6" t="n">
-        <v>7175258</v>
+        <v>7175322</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,12 +1214,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2000-01-01</t>
+          <t>2013-08-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2005-12-31</t>
+          <t>2013-08-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,6 +1228,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1226,22 +1240,22 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>per-erik mukka, Gudrun Norstedt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/297036</t>
+          <t>https://artportalen.se/Sighting/64659199</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73014862</v>
+        <v>297036</v>
       </c>
       <c r="B7" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,21 +1263,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1273,13 +1287,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>802911</v>
+        <v>802764</v>
       </c>
       <c r="R7" t="n">
-        <v>7175273</v>
+        <v>7175258</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1317,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
+          <t>2005-12-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,24 +1337,24 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73014862</t>
+          <t>https://artportalen.se/Sighting/297036</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73014863</v>
+        <v>73014862</v>
       </c>
       <c r="B8" t="n">
         <v>91909</v>
@@ -1375,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>803132</v>
+        <v>802911</v>
       </c>
       <c r="R8" t="n">
-        <v>7175354</v>
+        <v>7175273</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1436,13 +1450,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73014863</t>
+          <t>https://artportalen.se/Sighting/73014862</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120791525</v>
+        <v>73014863</v>
       </c>
       <c r="B9" t="n">
         <v>91909</v>
@@ -1473,17 +1487,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillavan, Vb</t>
+          <t>Kastfjärden, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>803222</v>
+        <v>803132</v>
       </c>
       <c r="R9" t="n">
-        <v>7175258</v>
+        <v>7175354</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,12 +1521,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,48 +1537,28 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lill Eilertsen</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lill Eilertsen</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120791525</t>
+          <t>https://artportalen.se/Sighting/73014863</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120791562</v>
+        <v>120791525</v>
       </c>
       <c r="B10" t="n">
         <v>91909</v>
@@ -1599,10 +1593,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>803016</v>
+        <v>803222</v>
       </c>
       <c r="R10" t="n">
-        <v>7175167</v>
+        <v>7175258</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1680,13 +1674,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120791562</t>
+          <t>https://artportalen.se/Sighting/120791525</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120791793</v>
+        <v>120791562</v>
       </c>
       <c r="B11" t="n">
         <v>91909</v>
@@ -1721,10 +1715,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>803117</v>
+        <v>803016</v>
       </c>
       <c r="R11" t="n">
-        <v>7175124</v>
+        <v>7175167</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1802,16 +1796,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120791793</t>
+          <t>https://artportalen.se/Sighting/120791562</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>64409355</v>
+        <v>120791793</v>
       </c>
       <c r="B12" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,40 +1813,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lillavan, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>803126</v>
+        <v>803117</v>
       </c>
       <c r="R12" t="n">
-        <v>7175328</v>
+        <v>7175124</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1876,12 +1867,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,22 +1883,4065 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Lill Eilertsen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Lill Eilertsen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/120791793</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135645786</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kastfjärden , Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>803074</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7175363</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135645786</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135688020</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>803063</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7175372</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135688020</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135688252</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>803058</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7175374</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135688252</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135688431</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>803098</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7175108</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135688431</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135688456</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>803106</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7175106</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135688456</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135710332</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kastfjärden, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>803214</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7175033</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135710332</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135710334</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kastfjärden, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>803222</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7175107</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135710334</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135710335</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kastfjärden, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>803229</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7175188</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135710335</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135710338</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kastfjärden, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>803200</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7175245</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135710338</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135710339</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kastfjärden, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>803115</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7175342</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135710339</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135710340</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kastfjärden, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>803099</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7175372</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135710340</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135710345</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kastfjärden, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>803061</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7175203</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135710345</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135688039</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92392</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>803063</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7175372</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>växte på ullticka, runda porer, utdragna mot kanten av lågan, fruktkroppen gulnade kraftigt efter torkning</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135688039</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135687531</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>803217</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7175187</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687531</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135687802</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79465</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>803151</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7175309</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687802</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135687873</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>803135</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7175325</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>äldre hackat hål i basen på en gran</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687873</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135687922</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>803129</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7175326</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>färskt hål i gran</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687922</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135688397</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>802998</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7175117</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>hål i högstubbe</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135688397</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>64409355</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lillavan, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>803126</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7175328</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2013-08-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2013-08-15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/64409355</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135645813</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kastfjärden , Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>803060</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7175371</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135645813</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135645839</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kastfjärden , Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>803088</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7175383</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135645839</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135645949</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kastfjärden , Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>803125</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7175289</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Födosök genom skalning av undertryckt gran</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135645949</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135687640</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>803157</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7175310</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>barksprätt på en gammal gran samt en barkskalad undertryckt gran</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687640</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135687713</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>803170</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7175011</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687713</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135687761</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>803200</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7175276</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687761</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135687832</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>803153</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7175319</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687832</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135688412</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>803078</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7175102</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135688412</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135688478</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>803122</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7175091</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135688478</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135710336</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kastfjärden, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>803217</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7175218</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack bild</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135710336</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135710347</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kastfjärden, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>803041</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7175192</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Skalad gran äldre</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135710347</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135710333</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kastfjärden, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>803214</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7175033</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135710333</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135710348</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kastfjärden, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>803118</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7175079</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135710348</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135645738</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kastfjärden , Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>803062</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7175366</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135645738</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135688282</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lill-Avan, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>803056</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7175365</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>ca 2x1 m med bladrosetter och 5st överblommade/blommande stänglar</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135688282</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135710342</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kastfjärden, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>803062</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7175357</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Överblommad, många bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135710342</t>
         </is>
       </c>
     </row>
@@ -1924,6 +5958,41 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48272-2024 artfynd.xlsx
+++ b/artfynd/A 48272-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135710343</v>
       </c>
       <c r="B3" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>135645786</v>
       </c>
       <c r="B13" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135688020</v>
       </c>
       <c r="B14" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>135688252</v>
       </c>
       <c r="B15" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>135688431</v>
       </c>
       <c r="B16" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135688456</v>
       </c>
       <c r="B17" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>135710332</v>
       </c>
       <c r="B18" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>135710334</v>
       </c>
       <c r="B19" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>135710335</v>
       </c>
       <c r="B20" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135710338</v>
       </c>
       <c r="B21" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135710339</v>
       </c>
       <c r="B22" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>135710340</v>
       </c>
       <c r="B23" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>135710345</v>
       </c>
       <c r="B24" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>135688039</v>
       </c>
       <c r="B25" t="n">
-        <v>92392</v>
+        <v>92394</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>135687531</v>
       </c>
       <c r="B26" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>135645738</v>
       </c>
       <c r="B45" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>135688282</v>
       </c>
       <c r="B46" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>135710342</v>
       </c>
       <c r="B47" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 48272-2024 artfynd.xlsx
+++ b/artfynd/A 48272-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135710343</v>
       </c>
       <c r="B3" t="n">
-        <v>92000</v>
+        <v>92014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>135645786</v>
       </c>
       <c r="B13" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135688020</v>
       </c>
       <c r="B14" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>135688252</v>
       </c>
       <c r="B15" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>135688431</v>
       </c>
       <c r="B16" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135688456</v>
       </c>
       <c r="B17" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>135710332</v>
       </c>
       <c r="B18" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>135710334</v>
       </c>
       <c r="B19" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>135710335</v>
       </c>
       <c r="B20" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135710338</v>
       </c>
       <c r="B21" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135710339</v>
       </c>
       <c r="B22" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>135710340</v>
       </c>
       <c r="B23" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>135710345</v>
       </c>
       <c r="B24" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>135688039</v>
       </c>
       <c r="B25" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>135687531</v>
       </c>
       <c r="B26" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>135687802</v>
       </c>
       <c r="B27" t="n">
-        <v>79465</v>
+        <v>79467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>135687873</v>
       </c>
       <c r="B28" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>135687922</v>
       </c>
       <c r="B29" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>135688397</v>
       </c>
       <c r="B30" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>135645813</v>
       </c>
       <c r="B32" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>135645839</v>
       </c>
       <c r="B33" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>135645949</v>
       </c>
       <c r="B34" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>135687640</v>
       </c>
       <c r="B35" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>135687713</v>
       </c>
       <c r="B36" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>135687761</v>
       </c>
       <c r="B37" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>135687832</v>
       </c>
       <c r="B38" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>135688412</v>
       </c>
       <c r="B39" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>135688478</v>
       </c>
       <c r="B40" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>135710336</v>
       </c>
       <c r="B41" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>135710347</v>
       </c>
       <c r="B42" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>135710333</v>
       </c>
       <c r="B43" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>135710348</v>
       </c>
       <c r="B44" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>135645738</v>
       </c>
       <c r="B45" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>135688282</v>
       </c>
       <c r="B46" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>135710342</v>
       </c>
       <c r="B47" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 48272-2024 artfynd.xlsx
+++ b/artfynd/A 48272-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135710343</v>
       </c>
       <c r="B3" t="n">
-        <v>92014</v>
+        <v>92015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>135645786</v>
       </c>
       <c r="B13" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135688020</v>
       </c>
       <c r="B14" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>135688252</v>
       </c>
       <c r="B15" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>135688431</v>
       </c>
       <c r="B16" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135688456</v>
       </c>
       <c r="B17" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>135710332</v>
       </c>
       <c r="B18" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>135710334</v>
       </c>
       <c r="B19" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>135710335</v>
       </c>
       <c r="B20" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135710338</v>
       </c>
       <c r="B21" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135710339</v>
       </c>
       <c r="B22" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>135710340</v>
       </c>
       <c r="B23" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>135710345</v>
       </c>
       <c r="B24" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>135688039</v>
       </c>
       <c r="B25" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>135687531</v>
       </c>
       <c r="B26" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>135687802</v>
       </c>
       <c r="B27" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>135645738</v>
       </c>
       <c r="B45" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>135688282</v>
       </c>
       <c r="B46" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>135710342</v>
       </c>
       <c r="B47" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 48272-2024 artfynd.xlsx
+++ b/artfynd/A 48272-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135710343</v>
       </c>
       <c r="B3" t="n">
-        <v>92015</v>
+        <v>92016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>135645786</v>
       </c>
       <c r="B13" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135688020</v>
       </c>
       <c r="B14" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>135688252</v>
       </c>
       <c r="B15" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>135688431</v>
       </c>
       <c r="B16" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135688456</v>
       </c>
       <c r="B17" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>135710332</v>
       </c>
       <c r="B18" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>135710334</v>
       </c>
       <c r="B19" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>135710335</v>
       </c>
       <c r="B20" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135710338</v>
       </c>
       <c r="B21" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135710339</v>
       </c>
       <c r="B22" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>135710340</v>
       </c>
       <c r="B23" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>135710345</v>
       </c>
       <c r="B24" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>135688039</v>
       </c>
       <c r="B25" t="n">
-        <v>92407</v>
+        <v>92408</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>135687531</v>
       </c>
       <c r="B26" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>135645738</v>
       </c>
       <c r="B45" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>135688282</v>
       </c>
       <c r="B46" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>135710342</v>
       </c>
       <c r="B47" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 48272-2024 artfynd.xlsx
+++ b/artfynd/A 48272-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135710343</v>
       </c>
       <c r="B3" t="n">
-        <v>92016</v>
+        <v>92017</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>135645786</v>
       </c>
       <c r="B13" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135688020</v>
       </c>
       <c r="B14" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>135688252</v>
       </c>
       <c r="B15" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>135688431</v>
       </c>
       <c r="B16" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135688456</v>
       </c>
       <c r="B17" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>135710332</v>
       </c>
       <c r="B18" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>135710334</v>
       </c>
       <c r="B19" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>135710335</v>
       </c>
       <c r="B20" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135710338</v>
       </c>
       <c r="B21" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135710339</v>
       </c>
       <c r="B22" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>135710340</v>
       </c>
       <c r="B23" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>135710345</v>
       </c>
       <c r="B24" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>135688039</v>
       </c>
       <c r="B25" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>135687531</v>
       </c>
       <c r="B26" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>135687802</v>
       </c>
       <c r="B27" t="n">
-        <v>79468</v>
+        <v>79469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>135687873</v>
       </c>
       <c r="B28" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>135687922</v>
       </c>
       <c r="B29" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>135688397</v>
       </c>
       <c r="B30" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>135645813</v>
       </c>
       <c r="B32" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>135645839</v>
       </c>
       <c r="B33" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>135645949</v>
       </c>
       <c r="B34" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>135687640</v>
       </c>
       <c r="B35" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>135687713</v>
       </c>
       <c r="B36" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>135687761</v>
       </c>
       <c r="B37" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>135687832</v>
       </c>
       <c r="B38" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>135688412</v>
       </c>
       <c r="B39" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>135688478</v>
       </c>
       <c r="B40" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>135710336</v>
       </c>
       <c r="B41" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>135710347</v>
       </c>
       <c r="B42" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>135710333</v>
       </c>
       <c r="B43" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>135710348</v>
       </c>
       <c r="B44" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>135645738</v>
       </c>
       <c r="B45" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>135688282</v>
       </c>
       <c r="B46" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>135710342</v>
       </c>
       <c r="B47" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 48272-2024 artfynd.xlsx
+++ b/artfynd/A 48272-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135710343</v>
       </c>
       <c r="B3" t="n">
-        <v>92017</v>
+        <v>92023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>135645786</v>
       </c>
       <c r="B13" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135688020</v>
       </c>
       <c r="B14" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>135688252</v>
       </c>
       <c r="B15" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>135688431</v>
       </c>
       <c r="B16" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135688456</v>
       </c>
       <c r="B17" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>135710332</v>
       </c>
       <c r="B18" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>135710334</v>
       </c>
       <c r="B19" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>135710335</v>
       </c>
       <c r="B20" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135710338</v>
       </c>
       <c r="B21" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135710339</v>
       </c>
       <c r="B22" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>135710340</v>
       </c>
       <c r="B23" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>135710345</v>
       </c>
       <c r="B24" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>135688039</v>
       </c>
       <c r="B25" t="n">
-        <v>92409</v>
+        <v>92415</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>135687531</v>
       </c>
       <c r="B26" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>135687802</v>
       </c>
       <c r="B27" t="n">
-        <v>79469</v>
+        <v>79473</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>135687873</v>
       </c>
       <c r="B28" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>135687922</v>
       </c>
       <c r="B29" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>135688397</v>
       </c>
       <c r="B30" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>135645813</v>
       </c>
       <c r="B32" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>135645839</v>
       </c>
       <c r="B33" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>135645949</v>
       </c>
       <c r="B34" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>135687640</v>
       </c>
       <c r="B35" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>135687713</v>
       </c>
       <c r="B36" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>135687761</v>
       </c>
       <c r="B37" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>135687832</v>
       </c>
       <c r="B38" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>135688412</v>
       </c>
       <c r="B39" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>135688478</v>
       </c>
       <c r="B40" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>135710336</v>
       </c>
       <c r="B41" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>135710347</v>
       </c>
       <c r="B42" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>135710333</v>
       </c>
       <c r="B43" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>135710348</v>
       </c>
       <c r="B44" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>135645738</v>
       </c>
       <c r="B45" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>135688282</v>
       </c>
       <c r="B46" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>135710342</v>
       </c>
       <c r="B47" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 48272-2024 artfynd.xlsx
+++ b/artfynd/A 48272-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135710343</v>
       </c>
       <c r="B3" t="n">
-        <v>92023</v>
+        <v>92024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135688020</v>
       </c>
       <c r="B14" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>135688252</v>
       </c>
       <c r="B15" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>135688431</v>
       </c>
       <c r="B16" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135688456</v>
       </c>
       <c r="B17" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>135710332</v>
       </c>
       <c r="B18" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>135710334</v>
       </c>
       <c r="B19" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>135710335</v>
       </c>
       <c r="B20" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135710338</v>
       </c>
       <c r="B21" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135710339</v>
       </c>
       <c r="B22" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>135710340</v>
       </c>
       <c r="B23" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>135710345</v>
       </c>
       <c r="B24" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>135688039</v>
       </c>
       <c r="B25" t="n">
-        <v>92415</v>
+        <v>92416</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>135687531</v>
       </c>
       <c r="B26" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>135687802</v>
       </c>
       <c r="B27" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>135687873</v>
       </c>
       <c r="B28" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>135687922</v>
       </c>
       <c r="B29" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>135688397</v>
       </c>
       <c r="B30" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>135687640</v>
       </c>
       <c r="B35" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>135687713</v>
       </c>
       <c r="B36" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>135687761</v>
       </c>
       <c r="B37" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>135687832</v>
       </c>
       <c r="B38" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>135688412</v>
       </c>
       <c r="B39" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>135688478</v>
       </c>
       <c r="B40" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>135710336</v>
       </c>
       <c r="B41" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>135710347</v>
       </c>
       <c r="B42" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>135710333</v>
       </c>
       <c r="B43" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>135710348</v>
       </c>
       <c r="B44" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>135688282</v>
       </c>
       <c r="B46" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>135710342</v>
       </c>
       <c r="B47" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 48272-2024 artfynd.xlsx
+++ b/artfynd/A 48272-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135710343</v>
       </c>
       <c r="B3" t="n">
-        <v>92024</v>
+        <v>92030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>135710332</v>
       </c>
       <c r="B18" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>135710334</v>
       </c>
       <c r="B19" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>135710335</v>
       </c>
       <c r="B20" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135710338</v>
       </c>
       <c r="B21" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135710339</v>
       </c>
       <c r="B22" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>135710340</v>
       </c>
       <c r="B23" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>135710345</v>
       </c>
       <c r="B24" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>135710342</v>
       </c>
       <c r="B47" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 48272-2024 artfynd.xlsx
+++ b/artfynd/A 48272-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135710343</v>
       </c>
       <c r="B3" t="n">
-        <v>92030</v>
+        <v>92037</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>135710332</v>
       </c>
       <c r="B18" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>135710334</v>
       </c>
       <c r="B19" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>135710335</v>
       </c>
       <c r="B20" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135710338</v>
       </c>
       <c r="B21" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135710339</v>
       </c>
       <c r="B22" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>135710340</v>
       </c>
       <c r="B23" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>135710345</v>
       </c>
       <c r="B24" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>135710336</v>
       </c>
       <c r="B41" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>135710347</v>
       </c>
       <c r="B42" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>135710333</v>
       </c>
       <c r="B43" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>135710348</v>
       </c>
       <c r="B44" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>135710342</v>
       </c>
       <c r="B47" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 48272-2024 artfynd.xlsx
+++ b/artfynd/A 48272-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>135710343</v>
       </c>
       <c r="B3" t="n">
-        <v>92037</v>
+        <v>92038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>135710332</v>
       </c>
       <c r="B18" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>135710334</v>
       </c>
       <c r="B19" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>135710335</v>
       </c>
       <c r="B20" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135710338</v>
       </c>
       <c r="B21" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135710339</v>
       </c>
       <c r="B22" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>135710340</v>
       </c>
       <c r="B23" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>135710345</v>
       </c>
       <c r="B24" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>135710342</v>
       </c>
       <c r="B47" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
